--- a/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
+++ b/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
@@ -427,7 +427,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="matrix.TbBasic" &amp; value_type="matrix.BasicRecord" &amp; index="id" &amp; mode="map" &amp; read_schema_from_file="false" &amp; output="matrix_tbbasic"</t>
+          <t>full_name="matrix.TbBasic" &amp; value_type="matrix.BasicRecord" &amp; index="id"</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="matrix.TbContainers" &amp; value_type="matrix.ContainerRecord" &amp; index="id" &amp; mode="map" &amp; read_schema_from_file="false" &amp; output="matrix_tbcontainers"</t>
+          <t>full_name="matrix.TbContainers" &amp; value_type="matrix.ContainerRecord" &amp; index="id"</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="matrix.TbMatrixSingleton" &amp; value_type="matrix.SingleConfig" &amp; mode="one" &amp; read_schema_from_file="false" &amp; output="matrix_tbmatrixsingleton"</t>
+          <t>full_name="matrix.TbMatrixSingleton" &amp; value_type="matrix.SingleConfig" &amp; mode="one"</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="matrix.TbMatrixList" &amp; value_type="matrix.ListRecord" &amp; mode="list" &amp; read_schema_from_file="false" &amp; output="matrix_tbmatrixlist"</t>
+          <t>full_name="matrix.TbMatrixList" &amp; value_type="matrix.ListRecord" &amp; mode="list"</t>
         </is>
       </c>
     </row>

--- a/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
+++ b/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Scenes/SampleScene.unity</t>
+          <t>Assets/Scenes/SampleScene.unity</t>
         </is>
       </c>
       <c r="G5" t="b">

--- a/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
+++ b/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="matrix.TbMatrixList" &amp; value_type="matrix.ListRecord" &amp; mode="list"</t>
+          <t>full_name="matrix.TbMatrixList" &amp; value_type="matrix.ListRecord" &amp; mode="list" &amp; output="matrix/nested/TbMatrixList"</t>
         </is>
       </c>
     </row>

--- a/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
+++ b/esyluban/examples/dev/DataTables/matrix/feature_tables.xlsx
@@ -427,7 +427,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="matrix.TbBasic" &amp; value_type="matrix.BasicRecord" &amp; index="id"</t>
+          <t>full_name="matrix.TbBasic" &amp; value_type="matrix.BasicRecord" &amp; index="id" &amp; group="c;s"</t>
         </is>
       </c>
     </row>
